--- a/database/event/8243/event_8243_evp_summary.xlsx
+++ b/database/event/8243/event_8243_evp_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EVP_Summary_8243" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVP_Summary_8243" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
         <v>3.9624</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4249</v>
+        <v>3.847</v>
       </c>
       <c r="E2" t="n">
         <v>10.5659</v>
@@ -548,7 +548,7 @@
         <v>3.5884</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0559</v>
+        <v>3.4441</v>
       </c>
       <c r="E3" t="n">
         <v>9.5686</v>
@@ -594,7 +594,7 @@
         <v>2.7111</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1903</v>
+        <v>2.4991</v>
       </c>
       <c r="E4" t="n">
         <v>7.2293</v>
@@ -640,7 +640,7 @@
         <v>2.5145</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9963</v>
+        <v>2.2873</v>
       </c>
       <c r="E5" t="n">
         <v>6.7049</v>
@@ -686,7 +686,7 @@
         <v>2.1286</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6156</v>
+        <v>1.8716</v>
       </c>
       <c r="E6" t="n">
         <v>5.6759</v>
@@ -732,7 +732,7 @@
         <v>2.1044</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5917</v>
+        <v>1.8456</v>
       </c>
       <c r="E7" t="n">
         <v>5.6115</v>
@@ -778,7 +778,7 @@
         <v>2.0584</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5464</v>
+        <v>1.796</v>
       </c>
       <c r="E8" t="n">
         <v>5.4889</v>
@@ -824,7 +824,7 @@
         <v>2.0468</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5349</v>
+        <v>1.7835</v>
       </c>
       <c r="E9" t="n">
         <v>5.4579</v>
@@ -870,7 +870,7 @@
         <v>1.8932</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3834</v>
+        <v>1.618</v>
       </c>
       <c r="E10" t="n">
         <v>5.0483</v>
@@ -916,7 +916,7 @@
         <v>1.6245</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1182</v>
+        <v>1.3285</v>
       </c>
       <c r="E11" t="n">
         <v>4.3317</v>
@@ -962,7 +962,7 @@
         <v>1.5629</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0575</v>
+        <v>1.2622</v>
       </c>
       <c r="E12" t="n">
         <v>4.1675</v>
@@ -1008,7 +1008,7 @@
         <v>1.5304</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0254</v>
+        <v>1.2272</v>
       </c>
       <c r="E13" t="n">
         <v>4.0809</v>
@@ -1054,7 +1054,7 @@
         <v>1.5141</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0094</v>
+        <v>1.2097</v>
       </c>
       <c r="E14" t="n">
         <v>4.0375</v>
@@ -1100,7 +1100,7 @@
         <v>1.3904</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8873</v>
+        <v>1.0764</v>
       </c>
       <c r="E15" t="n">
         <v>3.7076</v>
@@ -1146,7 +1146,7 @@
         <v>1.3885</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8854</v>
+        <v>1.0743</v>
       </c>
       <c r="E16" t="n">
         <v>3.7024</v>
@@ -1192,7 +1192,7 @@
         <v>1.378</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8751</v>
+        <v>1.0631</v>
       </c>
       <c r="E17" t="n">
         <v>3.6746</v>
@@ -1238,7 +1238,7 @@
         <v>1.2896</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.9678</v>
       </c>
       <c r="E18" t="n">
         <v>3.4388</v>
@@ -1284,7 +1284,7 @@
         <v>1.2247</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7238</v>
+        <v>0.8979</v>
       </c>
       <c r="E19" t="n">
         <v>3.2656</v>
@@ -1330,7 +1330,7 @@
         <v>1.2179</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7171</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="E20" t="n">
         <v>3.2475</v>
@@ -1376,7 +1376,7 @@
         <v>1.1347</v>
       </c>
       <c r="D21" t="n">
-        <v>0.635</v>
+        <v>0.801</v>
       </c>
       <c r="E21" t="n">
         <v>3.0258</v>
@@ -1422,7 +1422,7 @@
         <v>1.0449</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5464</v>
+        <v>0.7042</v>
       </c>
       <c r="E22" t="n">
         <v>2.7863</v>
@@ -1468,7 +1468,7 @@
         <v>0.9789</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4813</v>
+        <v>0.6331</v>
       </c>
       <c r="E23" t="n">
         <v>2.6102</v>
@@ -1514,7 +1514,7 @@
         <v>0.888</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3916</v>
+        <v>0.5353</v>
       </c>
       <c r="E24" t="n">
         <v>2.368</v>
@@ -1560,7 +1560,7 @@
         <v>0.8737</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3775</v>
+        <v>0.5198</v>
       </c>
       <c r="E25" t="n">
         <v>2.3298</v>
@@ -1606,7 +1606,7 @@
         <v>0.8712</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3751</v>
+        <v>0.5172</v>
       </c>
       <c r="E26" t="n">
         <v>2.3232</v>
@@ -1652,7 +1652,7 @@
         <v>0.8264</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3309</v>
+        <v>0.4689</v>
       </c>
       <c r="E27" t="n">
         <v>2.2037</v>
@@ -1698,7 +1698,7 @@
         <v>0.8082</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3129</v>
+        <v>0.4493</v>
       </c>
       <c r="E28" t="n">
         <v>2.1552</v>
@@ -1744,7 +1744,7 @@
         <v>0.7727000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2779</v>
+        <v>0.411</v>
       </c>
       <c r="E29" t="n">
         <v>2.0605</v>
@@ -1790,7 +1790,7 @@
         <v>0.7665999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2718</v>
+        <v>0.4044</v>
       </c>
       <c r="E30" t="n">
         <v>2.0441</v>
@@ -1836,7 +1836,7 @@
         <v>0.7584</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2637</v>
+        <v>0.3956</v>
       </c>
       <c r="E31" t="n">
         <v>2.0223</v>
@@ -1882,7 +1882,7 @@
         <v>0.6208</v>
       </c>
       <c r="D32" t="n">
-        <v>0.128</v>
+        <v>0.2474</v>
       </c>
       <c r="E32" t="n">
         <v>1.6555</v>
@@ -1928,7 +1928,7 @@
         <v>0.5796</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0873</v>
+        <v>0.203</v>
       </c>
       <c r="E33" t="n">
         <v>1.5455</v>
@@ -1974,7 +1974,7 @@
         <v>0.5184</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0269</v>
+        <v>0.1371</v>
       </c>
       <c r="E34" t="n">
         <v>1.3823</v>
@@ -2020,7 +2020,7 @@
         <v>0.5117</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0203</v>
+        <v>0.1299</v>
       </c>
       <c r="E35" t="n">
         <v>1.3645</v>
@@ -2066,7 +2066,7 @@
         <v>0.5084</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0171</v>
+        <v>0.1263</v>
       </c>
       <c r="E36" t="n">
         <v>1.3556</v>
@@ -2112,7 +2112,7 @@
         <v>0.483</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.008</v>
+        <v>0.0989</v>
       </c>
       <c r="E37" t="n">
         <v>1.2879</v>
@@ -2158,7 +2158,7 @@
         <v>0.4118</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.0222</v>
       </c>
       <c r="E38" t="n">
         <v>1.098</v>
@@ -2204,7 +2204,7 @@
         <v>0.2924</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.196</v>
+        <v>-0.1064</v>
       </c>
       <c r="E39" t="n">
         <v>0.7796999999999999</v>
@@ -2250,7 +2250,7 @@
         <v>0.2272</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2604</v>
+        <v>-0.1766</v>
       </c>
       <c r="E40" t="n">
         <v>0.6058</v>
@@ -2296,7 +2296,7 @@
         <v>0.205</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2823</v>
+        <v>-0.2005</v>
       </c>
       <c r="E41" t="n">
         <v>0.5466</v>
@@ -2342,7 +2342,7 @@
         <v>0.1053</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3806</v>
+        <v>-0.3079</v>
       </c>
       <c r="E42" t="n">
         <v>0.2809</v>
@@ -2388,7 +2388,7 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4054</v>
+        <v>-0.335</v>
       </c>
       <c r="E43" t="n">
         <v>0.2139</v>
@@ -2434,7 +2434,7 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4227</v>
+        <v>-0.3538</v>
       </c>
       <c r="E44" t="n">
         <v>0.1672</v>
@@ -2480,7 +2480,7 @@
         <v>0.0329</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4521</v>
+        <v>-0.3859</v>
       </c>
       <c r="E45" t="n">
         <v>0.0877</v>
@@ -2526,7 +2526,7 @@
         <v>0.0311</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4538</v>
+        <v>-0.3879</v>
       </c>
       <c r="E46" t="n">
         <v>0.0829</v>
@@ -2572,7 +2572,7 @@
         <v>0.0102</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4744</v>
+        <v>-0.4103</v>
       </c>
       <c r="E47" t="n">
         <v>0.0273</v>
@@ -2618,7 +2618,7 @@
         <v>-0.0256</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5098</v>
+        <v>-0.449</v>
       </c>
       <c r="E48" t="n">
         <v>-0.0683</v>
@@ -2664,7 +2664,7 @@
         <v>-0.0347</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5187</v>
+        <v>-0.4587</v>
       </c>
       <c r="E49" t="n">
         <v>-0.0925</v>
@@ -2710,7 +2710,7 @@
         <v>-0.0432</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5271</v>
+        <v>-0.4679</v>
       </c>
       <c r="E50" t="n">
         <v>-0.1151</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0459</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5298</v>
+        <v>-0.4708</v>
       </c>
       <c r="E51" t="n">
         <v>-0.1224</v>
@@ -2802,7 +2802,7 @@
         <v>-0.0563</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5401</v>
+        <v>-0.482</v>
       </c>
       <c r="E52" t="n">
         <v>-0.1501</v>
@@ -2848,7 +2848,7 @@
         <v>-0.062</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5457</v>
+        <v>-0.4881</v>
       </c>
       <c r="E53" t="n">
         <v>-0.1653</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0653</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-0.4917</v>
       </c>
       <c r="E54" t="n">
         <v>-0.174</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0679</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5515</v>
+        <v>-0.4945</v>
       </c>
       <c r="E55" t="n">
         <v>-0.181</v>
@@ -2986,7 +2986,7 @@
         <v>-0.0779</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5614</v>
+        <v>-0.5053</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2077</v>
@@ -3032,7 +3032,7 @@
         <v>-0.08160000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5092</v>
       </c>
       <c r="E57" t="n">
         <v>-0.2175</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1202</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6031</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="E58" t="n">
         <v>-0.3206</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1237</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6066</v>
+        <v>-0.5546</v>
       </c>
       <c r="E59" t="n">
         <v>-0.3299</v>
@@ -3170,7 +3170,7 @@
         <v>-0.1369</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6196</v>
+        <v>-0.5689</v>
       </c>
       <c r="E60" t="n">
         <v>-0.3651</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1913</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6733</v>
+        <v>-0.6274</v>
       </c>
       <c r="E61" t="n">
         <v>-0.5101</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2664</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7474</v>
+        <v>-0.7084</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7105</v>
@@ -3308,7 +3308,7 @@
         <v>-0.2722</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7531</v>
+        <v>-0.7146</v>
       </c>
       <c r="E63" t="n">
         <v>-0.7259</v>
@@ -3354,7 +3354,7 @@
         <v>-0.2725</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7534</v>
+        <v>-0.7149</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7267</v>
@@ -3400,7 +3400,7 @@
         <v>-0.2956</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7761</v>
+        <v>-0.7397</v>
       </c>
       <c r="E65" t="n">
         <v>-0.7881</v>
@@ -3446,7 +3446,7 @@
         <v>-0.3481</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.828</v>
+        <v>-0.7963</v>
       </c>
       <c r="E66" t="n">
         <v>-0.9282</v>
@@ -3492,7 +3492,7 @@
         <v>-0.3664</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.846</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9769</v>
@@ -3538,7 +3538,7 @@
         <v>-0.3721</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8517</v>
+        <v>-0.8222</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9923</v>
@@ -3584,7 +3584,7 @@
         <v>-0.3805</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.86</v>
+        <v>-0.8313</v>
       </c>
       <c r="E69" t="n">
         <v>-1.0147</v>
@@ -3630,7 +3630,7 @@
         <v>-0.4046</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8837</v>
+        <v>-0.8572</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0788</v>
@@ -3676,7 +3676,7 @@
         <v>-0.4549</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9334</v>
+        <v>-0.9114</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2131</v>
@@ -3722,7 +3722,7 @@
         <v>-0.4635</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9418</v>
+        <v>-0.9207</v>
       </c>
       <c r="E72" t="n">
         <v>-1.236</v>
@@ -3768,7 +3768,7 @@
         <v>-0.4734</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9516</v>
+        <v>-0.9313</v>
       </c>
       <c r="E73" t="n">
         <v>-1.2624</v>
@@ -3814,7 +3814,7 @@
         <v>-0.4833</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9614</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="E74" t="n">
         <v>-1.2888</v>
@@ -3860,7 +3860,7 @@
         <v>-0.5125</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9902</v>
+        <v>-0.9734</v>
       </c>
       <c r="E75" t="n">
         <v>-1.3666</v>
@@ -3906,7 +3906,7 @@
         <v>-0.5644</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0413</v>
+        <v>-1.0293</v>
       </c>
       <c r="E76" t="n">
         <v>-1.5049</v>
@@ -3952,7 +3952,7 @@
         <v>-0.6343</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1103</v>
+        <v>-1.1046</v>
       </c>
       <c r="E77" t="n">
         <v>-1.6913</v>
@@ -3998,7 +3998,7 @@
         <v>-0.75</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2245</v>
+        <v>-1.2293</v>
       </c>
       <c r="E78" t="n">
         <v>-2</v>
@@ -4044,7 +4044,7 @@
         <v>-1.1624</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.6314</v>
+        <v>-1.6736</v>
       </c>
       <c r="E79" t="n">
         <v>-3.0997</v>
@@ -4090,7 +4090,7 @@
         <v>-1.2125</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.6808</v>
+        <v>-1.7275</v>
       </c>
       <c r="E80" t="n">
         <v>-3.2333</v>
@@ -4136,7 +4136,7 @@
         <v>-1.2683</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7359</v>
+        <v>-1.7876</v>
       </c>
       <c r="E81" t="n">
         <v>-3.382</v>

--- a/database/event/8243/event_8243_evp_summary.xlsx
+++ b/database/event/8243/event_8243_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.9624</v>
       </c>
       <c r="D2" t="n">
-        <v>3.847</v>
+        <v>3.7655</v>
       </c>
       <c r="E2" t="n">
         <v>10.5659</v>
@@ -548,7 +548,7 @@
         <v>3.5884</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4441</v>
+        <v>3.3682</v>
       </c>
       <c r="E3" t="n">
         <v>9.5686</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.2293</v>
+        <v>7.2052</v>
       </c>
       <c r="C4" t="n">
-        <v>2.7111</v>
+        <v>2.7021</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4991</v>
+        <v>2.4266</v>
       </c>
       <c r="E4" t="n">
-        <v>7.2293</v>
+        <v>7.2052</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2373</v>
+        <v>3.2132</v>
       </c>
       <c r="G4" t="n">
         <v>3.992</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2373</v>
+        <v>3.2132</v>
       </c>
       <c r="I4" t="n">
         <v>3.2675</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.7049</v>
+        <v>6.6815</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5145</v>
+        <v>2.5057</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2873</v>
+        <v>2.218</v>
       </c>
       <c r="E5" t="n">
-        <v>6.7049</v>
+        <v>6.6815</v>
       </c>
       <c r="F5" t="n">
-        <v>4.6101</v>
+        <v>4.5867</v>
       </c>
       <c r="G5" t="n">
         <v>2.0948</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9256</v>
+        <v>4.8889</v>
       </c>
       <c r="I5" t="n">
         <v>4.9715</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.6759</v>
+        <v>5.6445</v>
       </c>
       <c r="C6" t="n">
-        <v>2.1286</v>
+        <v>2.1168</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8716</v>
+        <v>1.8049</v>
       </c>
       <c r="E6" t="n">
-        <v>5.6759</v>
+        <v>5.6445</v>
       </c>
       <c r="F6" t="n">
-        <v>5.6854</v>
+        <v>5.654</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0095</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6117</v>
+        <v>6.5624</v>
       </c>
       <c r="I6" t="n">
         <v>6.6734</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6115</v>
+        <v>5.5827</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1044</v>
+        <v>2.0936</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8456</v>
+        <v>1.7802</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6115</v>
+        <v>5.5827</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8672</v>
+        <v>3.8384</v>
       </c>
       <c r="G7" t="n">
         <v>1.7443</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8672</v>
+        <v>3.8384</v>
       </c>
       <c r="I7" t="n">
         <v>3.9033</v>
@@ -778,7 +778,7 @@
         <v>2.0584</v>
       </c>
       <c r="D8" t="n">
-        <v>1.796</v>
+        <v>1.7429</v>
       </c>
       <c r="E8" t="n">
         <v>5.4889</v>
@@ -824,7 +824,7 @@
         <v>2.0468</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7835</v>
+        <v>1.7305</v>
       </c>
       <c r="E9" t="n">
         <v>5.4579</v>
@@ -870,7 +870,7 @@
         <v>1.8932</v>
       </c>
       <c r="D10" t="n">
-        <v>1.618</v>
+        <v>1.5673</v>
       </c>
       <c r="E10" t="n">
         <v>5.0483</v>
@@ -916,7 +916,7 @@
         <v>1.6245</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3285</v>
+        <v>1.2818</v>
       </c>
       <c r="E11" t="n">
         <v>4.3317</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.1675</v>
+        <v>4.1432</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5629</v>
+        <v>1.5538</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2622</v>
+        <v>1.2067</v>
       </c>
       <c r="E12" t="n">
-        <v>4.1675</v>
+        <v>4.1432</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2635</v>
+        <v>3.2392</v>
       </c>
       <c r="G12" t="n">
         <v>0.904</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2635</v>
+        <v>3.2392</v>
       </c>
       <c r="I12" t="n">
         <v>3.294</v>
@@ -1008,7 +1008,7 @@
         <v>1.5304</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2272</v>
+        <v>1.1819</v>
       </c>
       <c r="E13" t="n">
         <v>4.0809</v>
@@ -1054,7 +1054,7 @@
         <v>1.5141</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2097</v>
+        <v>1.1646</v>
       </c>
       <c r="E14" t="n">
         <v>4.0375</v>
@@ -1100,7 +1100,7 @@
         <v>1.3904</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0764</v>
+        <v>1.0332</v>
       </c>
       <c r="E15" t="n">
         <v>3.7076</v>
@@ -1146,7 +1146,7 @@
         <v>1.3885</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0743</v>
+        <v>1.0311</v>
       </c>
       <c r="E16" t="n">
         <v>3.7024</v>
@@ -1192,7 +1192,7 @@
         <v>1.378</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0631</v>
+        <v>1.0201</v>
       </c>
       <c r="E17" t="n">
         <v>3.6746</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.4388</v>
+        <v>3.414</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2896</v>
+        <v>1.2803</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9678</v>
+        <v>0.9162</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4388</v>
+        <v>3.414</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3183</v>
+        <v>3.2935</v>
       </c>
       <c r="G18" t="n">
         <v>0.1205</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3183</v>
+        <v>3.2935</v>
       </c>
       <c r="I18" t="n">
         <v>3.3492</v>
@@ -1284,7 +1284,7 @@
         <v>1.2247</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8979</v>
+        <v>0.8571</v>
       </c>
       <c r="E19" t="n">
         <v>3.2656</v>
@@ -1330,7 +1330,7 @@
         <v>1.2179</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.8499</v>
       </c>
       <c r="E20" t="n">
         <v>3.2475</v>
@@ -1376,7 +1376,7 @@
         <v>1.1347</v>
       </c>
       <c r="D21" t="n">
-        <v>0.801</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="E21" t="n">
         <v>3.0258</v>
@@ -1422,7 +1422,7 @@
         <v>1.0449</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7042</v>
+        <v>0.6662</v>
       </c>
       <c r="E22" t="n">
         <v>2.7863</v>
@@ -1468,7 +1468,7 @@
         <v>0.9789</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6331</v>
+        <v>0.596</v>
       </c>
       <c r="E23" t="n">
         <v>2.6102</v>
@@ -1514,7 +1514,7 @@
         <v>0.888</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5353</v>
+        <v>0.4995</v>
       </c>
       <c r="E24" t="n">
         <v>2.368</v>
@@ -1560,7 +1560,7 @@
         <v>0.8737</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5198</v>
+        <v>0.4843</v>
       </c>
       <c r="E25" t="n">
         <v>2.3298</v>
@@ -1606,7 +1606,7 @@
         <v>0.8712</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5172</v>
+        <v>0.4817</v>
       </c>
       <c r="E26" t="n">
         <v>2.3232</v>
@@ -1652,7 +1652,7 @@
         <v>0.8264</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4689</v>
+        <v>0.434</v>
       </c>
       <c r="E27" t="n">
         <v>2.2037</v>
@@ -1698,7 +1698,7 @@
         <v>0.8082</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4493</v>
+        <v>0.4147</v>
       </c>
       <c r="E28" t="n">
         <v>2.1552</v>
@@ -1744,7 +1744,7 @@
         <v>0.7727000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0.411</v>
+        <v>0.377</v>
       </c>
       <c r="E29" t="n">
         <v>2.0605</v>
@@ -1790,7 +1790,7 @@
         <v>0.7665999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4044</v>
+        <v>0.3705</v>
       </c>
       <c r="E30" t="n">
         <v>2.0441</v>
@@ -1836,7 +1836,7 @@
         <v>0.7584</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3956</v>
+        <v>0.3618</v>
       </c>
       <c r="E31" t="n">
         <v>2.0223</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.6555</v>
+        <v>1.6357</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6208</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2474</v>
+        <v>0.2078</v>
       </c>
       <c r="E32" t="n">
-        <v>1.6555</v>
+        <v>1.6357</v>
       </c>
       <c r="F32" t="n">
-        <v>2.6555</v>
+        <v>2.6357</v>
       </c>
       <c r="G32" t="n">
         <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>2.6555</v>
+        <v>2.6357</v>
       </c>
       <c r="I32" t="n">
         <v>2.6803</v>
@@ -1928,7 +1928,7 @@
         <v>0.5796</v>
       </c>
       <c r="D33" t="n">
-        <v>0.203</v>
+        <v>0.1718</v>
       </c>
       <c r="E33" t="n">
         <v>1.5455</v>
@@ -1974,7 +1974,7 @@
         <v>0.5184</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1371</v>
+        <v>0.1068</v>
       </c>
       <c r="E34" t="n">
         <v>1.3823</v>
@@ -2020,7 +2020,7 @@
         <v>0.5117</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1299</v>
+        <v>0.0997</v>
       </c>
       <c r="E35" t="n">
         <v>1.3645</v>
@@ -2066,7 +2066,7 @@
         <v>0.5084</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1263</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="E36" t="n">
         <v>1.3556</v>
@@ -2112,7 +2112,7 @@
         <v>0.483</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0989</v>
+        <v>0.0692</v>
       </c>
       <c r="E37" t="n">
         <v>1.2879</v>
@@ -2158,7 +2158,7 @@
         <v>0.4118</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0222</v>
+        <v>-0.0065</v>
       </c>
       <c r="E38" t="n">
         <v>1.098</v>
@@ -2204,7 +2204,7 @@
         <v>0.2924</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1064</v>
+        <v>-0.1333</v>
       </c>
       <c r="E39" t="n">
         <v>0.7796999999999999</v>
@@ -2250,7 +2250,7 @@
         <v>0.2272</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1766</v>
+        <v>-0.2026</v>
       </c>
       <c r="E40" t="n">
         <v>0.6058</v>
@@ -2296,7 +2296,7 @@
         <v>0.205</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2005</v>
+        <v>-0.2261</v>
       </c>
       <c r="E41" t="n">
         <v>0.5466</v>
@@ -2342,7 +2342,7 @@
         <v>0.1053</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3079</v>
+        <v>-0.332</v>
       </c>
       <c r="E42" t="n">
         <v>0.2809</v>
@@ -2388,7 +2388,7 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.335</v>
+        <v>-0.3587</v>
       </c>
       <c r="E43" t="n">
         <v>0.2139</v>
@@ -2434,7 +2434,7 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3538</v>
+        <v>-0.3773</v>
       </c>
       <c r="E44" t="n">
         <v>0.1672</v>
@@ -2480,7 +2480,7 @@
         <v>0.0329</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3859</v>
+        <v>-0.409</v>
       </c>
       <c r="E45" t="n">
         <v>0.0877</v>
@@ -2526,7 +2526,7 @@
         <v>0.0311</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3879</v>
+        <v>-0.4109</v>
       </c>
       <c r="E46" t="n">
         <v>0.0829</v>
@@ -2572,7 +2572,7 @@
         <v>0.0102</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4103</v>
+        <v>-0.433</v>
       </c>
       <c r="E47" t="n">
         <v>0.0273</v>
@@ -2618,7 +2618,7 @@
         <v>-0.0256</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.449</v>
+        <v>-0.4711</v>
       </c>
       <c r="E48" t="n">
         <v>-0.0683</v>
@@ -2664,7 +2664,7 @@
         <v>-0.0347</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4587</v>
+        <v>-0.4808</v>
       </c>
       <c r="E49" t="n">
         <v>-0.0925</v>
@@ -2710,7 +2710,7 @@
         <v>-0.0432</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4679</v>
+        <v>-0.4898</v>
       </c>
       <c r="E50" t="n">
         <v>-0.1151</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0459</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4708</v>
+        <v>-0.4927</v>
       </c>
       <c r="E51" t="n">
         <v>-0.1224</v>
@@ -2802,7 +2802,7 @@
         <v>-0.0563</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.482</v>
+        <v>-0.5037</v>
       </c>
       <c r="E52" t="n">
         <v>-0.1501</v>
@@ -2848,7 +2848,7 @@
         <v>-0.062</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4881</v>
+        <v>-0.5098</v>
       </c>
       <c r="E53" t="n">
         <v>-0.1653</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0653</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4917</v>
+        <v>-0.5132</v>
       </c>
       <c r="E54" t="n">
         <v>-0.174</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0679</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4945</v>
+        <v>-0.516</v>
       </c>
       <c r="E55" t="n">
         <v>-0.181</v>
@@ -2986,7 +2986,7 @@
         <v>-0.0779</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5053</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2077</v>
@@ -3032,7 +3032,7 @@
         <v>-0.08160000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5092</v>
+        <v>-0.5306</v>
       </c>
       <c r="E57" t="n">
         <v>-0.2175</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3206</v>
+        <v>-0.3257</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1202</v>
+        <v>-0.1221</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.5737</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3206</v>
+        <v>-0.3257</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6794</v>
+        <v>0.6743</v>
       </c>
       <c r="G58" t="n">
         <v>-1</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6794</v>
+        <v>0.6743</v>
       </c>
       <c r="I58" t="n">
         <v>0.6857</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1237</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5546</v>
+        <v>-0.5753</v>
       </c>
       <c r="E59" t="n">
         <v>-0.3299</v>
@@ -3170,7 +3170,7 @@
         <v>-0.1369</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5689</v>
+        <v>-0.5894</v>
       </c>
       <c r="E60" t="n">
         <v>-0.3651</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5101</v>
+        <v>-0.507</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1913</v>
+        <v>-0.1901</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6274</v>
+        <v>-0.6459</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5101</v>
+        <v>-0.507</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.4189</v>
+        <v>-0.4158</v>
       </c>
       <c r="G61" t="n">
         <v>-0.0912</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.4189</v>
+        <v>-0.4158</v>
       </c>
       <c r="I61" t="n">
         <v>-0.4228</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2664</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7084</v>
+        <v>-0.727</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7105</v>
@@ -3308,7 +3308,7 @@
         <v>-0.2722</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7146</v>
+        <v>-0.7331</v>
       </c>
       <c r="E63" t="n">
         <v>-0.7259</v>
@@ -3354,7 +3354,7 @@
         <v>-0.2725</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7149</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7267</v>
@@ -3400,7 +3400,7 @@
         <v>-0.2956</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7397</v>
+        <v>-0.7579</v>
       </c>
       <c r="E65" t="n">
         <v>-0.7881</v>
@@ -3446,7 +3446,7 @@
         <v>-0.3481</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7963</v>
+        <v>-0.8137</v>
       </c>
       <c r="E66" t="n">
         <v>-0.9282</v>
@@ -3492,7 +3492,7 @@
         <v>-0.3664</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.8331</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9769</v>
@@ -3538,7 +3538,7 @@
         <v>-0.3721</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8222</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9923</v>
@@ -3584,7 +3584,7 @@
         <v>-0.3805</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8313</v>
+        <v>-0.8482</v>
       </c>
       <c r="E69" t="n">
         <v>-1.0147</v>
@@ -3630,7 +3630,7 @@
         <v>-0.4046</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8572</v>
+        <v>-0.8737</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0788</v>
@@ -3676,7 +3676,7 @@
         <v>-0.4549</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9114</v>
+        <v>-0.9272</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2131</v>
@@ -3722,7 +3722,7 @@
         <v>-0.4635</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9207</v>
+        <v>-0.9363</v>
       </c>
       <c r="E72" t="n">
         <v>-1.236</v>
@@ -3768,7 +3768,7 @@
         <v>-0.4734</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9313</v>
+        <v>-0.9469</v>
       </c>
       <c r="E73" t="n">
         <v>-1.2624</v>
@@ -3814,7 +3814,7 @@
         <v>-0.4833</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.9574</v>
       </c>
       <c r="E74" t="n">
         <v>-1.2888</v>
@@ -3860,7 +3860,7 @@
         <v>-0.5125</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9734</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="E75" t="n">
         <v>-1.3666</v>
@@ -3906,7 +3906,7 @@
         <v>-0.5644</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0293</v>
+        <v>-1.0435</v>
       </c>
       <c r="E76" t="n">
         <v>-1.5049</v>
@@ -3952,7 +3952,7 @@
         <v>-0.6343</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1046</v>
+        <v>-1.1177</v>
       </c>
       <c r="E77" t="n">
         <v>-1.6913</v>
@@ -3998,7 +3998,7 @@
         <v>-0.75</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E78" t="n">
         <v>-2</v>
@@ -4044,7 +4044,7 @@
         <v>-1.1624</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.6736</v>
+        <v>-1.6788</v>
       </c>
       <c r="E79" t="n">
         <v>-3.0997</v>
@@ -4090,7 +4090,7 @@
         <v>-1.2125</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.7275</v>
+        <v>-1.7321</v>
       </c>
       <c r="E80" t="n">
         <v>-3.2333</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.382</v>
+        <v>-3.3759</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.2683</v>
+        <v>-1.266</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7876</v>
+        <v>-1.7889</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.382</v>
+        <v>-3.3759</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.8084</v>
+        <v>-0.8023</v>
       </c>
       <c r="G81" t="n">
         <v>-2.5736</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.8084</v>
+        <v>-0.8023</v>
       </c>
       <c r="I81" t="n">
         <v>-0.8159</v>

--- a/database/event/8243/event_8243_evp_summary.xlsx
+++ b/database/event/8243/event_8243_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.4824</v>
+        <v>9.823600000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5561</v>
+        <v>3.684</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6924</v>
+        <v>3.7742</v>
       </c>
       <c r="E2" t="n">
-        <v>9.4824</v>
+        <v>9.823600000000001</v>
       </c>
       <c r="F2" t="n">
         <v>3.2863</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.847200000000001</v>
+        <v>8.9941</v>
       </c>
       <c r="C3" t="n">
-        <v>3.3179</v>
+        <v>3.3729</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4032</v>
+        <v>3.4036</v>
       </c>
       <c r="E3" t="n">
-        <v>8.847200000000001</v>
+        <v>8.9941</v>
       </c>
       <c r="F3" t="n">
         <v>2.6739</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.1606</v>
+        <v>7.2407</v>
       </c>
       <c r="C4" t="n">
-        <v>2.6853</v>
+        <v>2.7154</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6354</v>
+        <v>2.6204</v>
       </c>
       <c r="E4" t="n">
-        <v>7.1606</v>
+        <v>7.2407</v>
       </c>
       <c r="F4" t="n">
         <v>3.2268</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.9285</v>
+        <v>5.9654</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2233</v>
+        <v>2.2371</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0746</v>
+        <v>2.0508</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9285</v>
+        <v>5.9654</v>
       </c>
       <c r="F5" t="n">
         <v>2.0004</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3746</v>
+        <v>5.4396</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0156</v>
+        <v>2.0399</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8224</v>
+        <v>1.8159</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3746</v>
+        <v>5.4396</v>
       </c>
       <c r="F6" t="n">
         <v>3.5261</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.8374</v>
+        <v>5.118</v>
       </c>
       <c r="C7" t="n">
-        <v>1.8141</v>
+        <v>1.9193</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5779</v>
+        <v>1.6723</v>
       </c>
       <c r="E7" t="n">
-        <v>4.8374</v>
+        <v>5.118</v>
       </c>
       <c r="F7" t="n">
         <v>4.5807</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.8023</v>
+        <v>5.0285</v>
       </c>
       <c r="C8" t="n">
-        <v>1.8009</v>
+        <v>1.8858</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5619</v>
+        <v>1.6323</v>
       </c>
       <c r="E8" t="n">
-        <v>4.8023</v>
+        <v>5.0285</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1863</v>
+        <v>4.5856</v>
       </c>
       <c r="G8" t="n">
-        <v>1.616</v>
+        <v>0.1018</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2489</v>
+        <v>7.3114</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4707</v>
+        <v>7.6931</v>
       </c>
       <c r="J8" t="n">
-        <v>1.616</v>
+        <v>0.1018</v>
       </c>
       <c r="K8" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="L8" t="n">
-        <v>183</v>
+        <v>64</v>
       </c>
       <c r="M8" t="n">
-        <v>6.0867</v>
+        <v>7.7949</v>
       </c>
       <c r="N8" t="n">
-        <v>382</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.6874</v>
+        <v>4.8509</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7579</v>
+        <v>1.8192</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5096</v>
+        <v>1.553</v>
       </c>
       <c r="E9" t="n">
-        <v>4.6874</v>
+        <v>4.8509</v>
       </c>
       <c r="F9" t="n">
-        <v>4.5856</v>
+        <v>3.1863</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1018</v>
+        <v>1.616</v>
       </c>
       <c r="H9" t="n">
-        <v>7.3114</v>
+        <v>4.2489</v>
       </c>
       <c r="I9" t="n">
-        <v>7.6931</v>
+        <v>4.4707</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1018</v>
+        <v>1.616</v>
       </c>
       <c r="K9" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L9" t="n">
-        <v>64</v>
+        <v>183</v>
       </c>
       <c r="M9" t="n">
-        <v>7.7949</v>
+        <v>6.0867</v>
       </c>
       <c r="N9" t="n">
-        <v>259</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.6168</v>
+        <v>4.7674</v>
       </c>
       <c r="C10" t="n">
-        <v>1.7314</v>
+        <v>1.7879</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4775</v>
+        <v>1.5157</v>
       </c>
       <c r="E10" t="n">
-        <v>4.6168</v>
+        <v>4.7674</v>
       </c>
       <c r="F10" t="n">
         <v>3.5395</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.5415</v>
+        <v>4.6723</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7031</v>
+        <v>1.7522</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4432</v>
+        <v>1.4732</v>
       </c>
       <c r="E11" t="n">
-        <v>4.5415</v>
+        <v>4.6723</v>
       </c>
       <c r="F11" t="n">
         <v>3.2825</v>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.0515</v>
+        <v>4.2832</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5194</v>
+        <v>1.6063</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2201</v>
+        <v>1.2994</v>
       </c>
       <c r="E12" t="n">
-        <v>4.0515</v>
+        <v>4.2832</v>
       </c>
       <c r="F12" t="n">
         <v>4.2804</v>
@@ -998,127 +998,127 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.9986</v>
+        <v>4.017</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4995</v>
+        <v>1.5064</v>
       </c>
       <c r="D13" t="n">
-        <v>1.196</v>
+        <v>1.1805</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9986</v>
+        <v>4.017</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0456</v>
+        <v>1.4212</v>
       </c>
       <c r="G13" t="n">
-        <v>0.953</v>
+        <v>2.5599</v>
       </c>
       <c r="H13" t="n">
-        <v>5.1545</v>
+        <v>1.4212</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7834</v>
+        <v>1.4212</v>
       </c>
       <c r="J13" t="n">
-        <v>0.953</v>
+        <v>2.5599</v>
       </c>
       <c r="K13" t="n">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="L13" t="n">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7364</v>
+        <v>3.9811</v>
       </c>
       <c r="N13" t="n">
-        <v>232</v>
+        <v>336</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.9811</v>
+        <v>3.9855</v>
       </c>
       <c r="C14" t="n">
-        <v>1.493</v>
+        <v>1.4946</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1881</v>
+        <v>1.1664</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9811</v>
+        <v>3.9855</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4212</v>
+        <v>3.9984</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5599</v>
+        <v>-0.0789</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4212</v>
+        <v>8.2979</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4212</v>
+        <v>4.4808</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5599</v>
+        <v>-0.0789</v>
       </c>
       <c r="K14" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="L14" t="n">
-        <v>171</v>
+        <v>57</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9811</v>
+        <v>4.4019</v>
       </c>
       <c r="N14" t="n">
-        <v>336</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.9195</v>
+        <v>3.9809</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4699</v>
+        <v>1.4929</v>
       </c>
       <c r="D15" t="n">
-        <v>1.16</v>
+        <v>1.1644</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9195</v>
+        <v>3.9809</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9984</v>
+        <v>3.0456</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0789</v>
+        <v>0.953</v>
       </c>
       <c r="H15" t="n">
-        <v>8.2979</v>
+        <v>5.1545</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4808</v>
+        <v>2.7834</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0789</v>
+        <v>0.953</v>
       </c>
       <c r="K15" t="n">
         <v>175</v>
@@ -1127,7 +1127,7 @@
         <v>57</v>
       </c>
       <c r="M15" t="n">
-        <v>4.4019</v>
+        <v>3.7364</v>
       </c>
       <c r="N15" t="n">
         <v>232</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.8114</v>
+        <v>3.9589</v>
       </c>
       <c r="C16" t="n">
-        <v>1.4293</v>
+        <v>1.4847</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1108</v>
+        <v>1.1545</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8114</v>
+        <v>3.9589</v>
       </c>
       <c r="F16" t="n">
         <v>4.5807</v>
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.4974</v>
+        <v>3.9061</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3116</v>
+        <v>1.4649</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9679</v>
+        <v>1.1309</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4974</v>
+        <v>3.9061</v>
       </c>
       <c r="F17" t="n">
         <v>2.7075</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.222</v>
+        <v>3.3204</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2083</v>
+        <v>1.2452</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8425</v>
+        <v>0.8693</v>
       </c>
       <c r="E18" t="n">
-        <v>3.222</v>
+        <v>3.3204</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8828</v>
+        <v>3.0868</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3392</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5846</v>
+        <v>4.0312</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7717</v>
+        <v>4.0312</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3392</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="L18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1109</v>
+        <v>4.0312</v>
       </c>
       <c r="N18" t="n">
-        <v>259</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.0868</v>
+        <v>3.2799</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1576</v>
+        <v>1.23</v>
       </c>
       <c r="D19" t="n">
-        <v>0.781</v>
+        <v>0.8512</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0868</v>
+        <v>3.2799</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0868</v>
+        <v>2.8828</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.3392</v>
       </c>
       <c r="H19" t="n">
-        <v>4.0312</v>
+        <v>3.5846</v>
       </c>
       <c r="I19" t="n">
-        <v>4.0312</v>
+        <v>3.7717</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.3392</v>
       </c>
       <c r="K19" t="n">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M19" t="n">
-        <v>4.0312</v>
+        <v>4.1109</v>
       </c>
       <c r="N19" t="n">
-        <v>163</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20">
@@ -1324,16 +1324,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.0606</v>
+        <v>3.262</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1478</v>
+        <v>1.2233</v>
       </c>
       <c r="D20" t="n">
-        <v>0.769</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>3.0606</v>
+        <v>3.262</v>
       </c>
       <c r="F20" t="n">
         <v>3.0606</v>
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.05</v>
+        <v>3.2497</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1438</v>
+        <v>1.2187</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7642</v>
+        <v>0.8377</v>
       </c>
       <c r="E21" t="n">
-        <v>3.05</v>
+        <v>3.2497</v>
       </c>
       <c r="F21" t="n">
         <v>2.4011</v>
@@ -1412,415 +1412,415 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>s1zzi</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.0029</v>
+        <v>3.1086</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1261</v>
+        <v>1.1658</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7428</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>3.0029</v>
+        <v>3.1086</v>
       </c>
       <c r="F22" t="n">
-        <v>2.975</v>
+        <v>2.932</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0279</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>4.9213</v>
+        <v>3.6922</v>
       </c>
       <c r="I22" t="n">
-        <v>2.6574</v>
+        <v>3.6922</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0279</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="L22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.6853</v>
+        <v>3.6922</v>
       </c>
       <c r="N22" t="n">
-        <v>268</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>s1zzi</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.932</v>
+        <v>3.0779</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0996</v>
+        <v>1.1543</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7105</v>
+        <v>0.761</v>
       </c>
       <c r="E23" t="n">
-        <v>2.932</v>
+        <v>3.0779</v>
       </c>
       <c r="F23" t="n">
-        <v>2.932</v>
+        <v>2.8839</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.6922</v>
+        <v>3.587</v>
       </c>
       <c r="I23" t="n">
-        <v>3.6922</v>
+        <v>3.587</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6922</v>
+        <v>3.587</v>
       </c>
       <c r="N23" t="n">
-        <v>191</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.8839</v>
+        <v>3.033</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0815</v>
+        <v>1.1374</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6886</v>
+        <v>0.741</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8839</v>
+        <v>3.033</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8839</v>
+        <v>2.975</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.0279</v>
       </c>
       <c r="H24" t="n">
-        <v>3.587</v>
+        <v>4.9213</v>
       </c>
       <c r="I24" t="n">
-        <v>3.587</v>
+        <v>2.6574</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.0279</v>
       </c>
       <c r="K24" t="n">
-        <v>163</v>
+        <v>228</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M24" t="n">
-        <v>3.587</v>
+        <v>2.6853</v>
       </c>
       <c r="N24" t="n">
-        <v>163</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.7123</v>
+        <v>2.9522</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0172</v>
+        <v>1.1071</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6105</v>
+        <v>0.7049</v>
       </c>
       <c r="E25" t="n">
-        <v>2.7123</v>
+        <v>2.9522</v>
       </c>
       <c r="F25" t="n">
-        <v>2.7123</v>
+        <v>2.6763</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2114</v>
+        <v>3.1326</v>
       </c>
       <c r="I25" t="n">
-        <v>3.2114</v>
+        <v>3.1326</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2114</v>
+        <v>3.1326</v>
       </c>
       <c r="N25" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.6763</v>
+        <v>2.8262</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0037</v>
+        <v>1.0599</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5941</v>
+        <v>0.6486</v>
       </c>
       <c r="E26" t="n">
-        <v>2.6763</v>
+        <v>2.8262</v>
       </c>
       <c r="F26" t="n">
-        <v>2.6763</v>
+        <v>2.5949</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3.1326</v>
+        <v>2.9545</v>
       </c>
       <c r="I26" t="n">
-        <v>3.1326</v>
+        <v>2.9545</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>138</v>
+        <v>191</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1326</v>
+        <v>2.9545</v>
       </c>
       <c r="N26" t="n">
-        <v>138</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dziugss</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.6336</v>
+        <v>2.8222</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9876</v>
+        <v>1.0584</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5747</v>
+        <v>0.6468</v>
       </c>
       <c r="E27" t="n">
-        <v>2.6336</v>
+        <v>2.8222</v>
       </c>
       <c r="F27" t="n">
-        <v>2.6336</v>
+        <v>2.7123</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3.0392</v>
+        <v>3.2114</v>
       </c>
       <c r="I27" t="n">
-        <v>3.0392</v>
+        <v>3.2114</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.0392</v>
+        <v>3.2114</v>
       </c>
       <c r="N27" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>dziugss</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.5949</v>
+        <v>2.6891</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9731</v>
+        <v>1.0085</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5873</v>
       </c>
       <c r="E28" t="n">
-        <v>2.5949</v>
+        <v>2.6891</v>
       </c>
       <c r="F28" t="n">
-        <v>2.5949</v>
+        <v>2.6336</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.9545</v>
+        <v>3.0392</v>
       </c>
       <c r="I28" t="n">
-        <v>2.9545</v>
+        <v>3.0392</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.9545</v>
+        <v>3.0392</v>
       </c>
       <c r="N28" t="n">
-        <v>191</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SHOCK</t>
+          <t>Kvem</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.365</v>
+        <v>2.6522</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8869</v>
+        <v>0.9946</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4524</v>
+        <v>0.5709</v>
       </c>
       <c r="E29" t="n">
-        <v>2.365</v>
+        <v>2.6522</v>
       </c>
       <c r="F29" t="n">
-        <v>2.365</v>
+        <v>2.2909</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.4513</v>
+        <v>2.2909</v>
       </c>
       <c r="I29" t="n">
-        <v>2.4513</v>
+        <v>2.2909</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.4513</v>
+        <v>2.2909</v>
       </c>
       <c r="N29" t="n">
-        <v>175</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kvem</t>
+          <t>SHOCK</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.2909</v>
+        <v>2.4273</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8591</v>
+        <v>0.9103</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4187</v>
+        <v>0.4704</v>
       </c>
       <c r="E30" t="n">
-        <v>2.2909</v>
+        <v>2.4273</v>
       </c>
       <c r="F30" t="n">
-        <v>2.2909</v>
+        <v>2.365</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2909</v>
+        <v>2.4513</v>
       </c>
       <c r="I30" t="n">
-        <v>2.2909</v>
+        <v>2.4513</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.2909</v>
+        <v>2.4513</v>
       </c>
       <c r="N30" t="n">
-        <v>110</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31">
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.013</v>
+        <v>2.0582</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7549</v>
+        <v>0.7719</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2922</v>
+        <v>0.3055</v>
       </c>
       <c r="E31" t="n">
-        <v>2.013</v>
+        <v>2.0582</v>
       </c>
       <c r="F31" t="n">
         <v>2.013</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.875</v>
+        <v>1.9916</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7032</v>
+        <v>0.7469</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2293</v>
+        <v>0.2758</v>
       </c>
       <c r="E32" t="n">
-        <v>1.875</v>
+        <v>1.9916</v>
       </c>
       <c r="F32" t="n">
-        <v>1.875</v>
+        <v>1.6939</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.875</v>
+        <v>1.6939</v>
       </c>
       <c r="I32" t="n">
-        <v>1.875</v>
+        <v>1.6939</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.875</v>
+        <v>1.6939</v>
       </c>
       <c r="N32" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.8022</v>
+        <v>1.9833</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.7438</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1962</v>
+        <v>0.2721</v>
       </c>
       <c r="E33" t="n">
-        <v>1.8022</v>
+        <v>1.9833</v>
       </c>
       <c r="F33" t="n">
-        <v>2.3332</v>
+        <v>1.875</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.531</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.8039</v>
+        <v>1.875</v>
       </c>
       <c r="I33" t="n">
-        <v>1.5141</v>
+        <v>1.875</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.531</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>228</v>
+        <v>163</v>
       </c>
       <c r="L33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9831</v>
+        <v>1.875</v>
       </c>
       <c r="N33" t="n">
-        <v>268</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34">
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.7956</v>
+        <v>1.7918</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6734</v>
+        <v>0.672</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1932</v>
+        <v>0.1865</v>
       </c>
       <c r="E34" t="n">
-        <v>1.7956</v>
+        <v>1.7918</v>
       </c>
       <c r="F34" t="n">
         <v>1.0281</v>
@@ -2010,139 +2010,139 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>kisserek</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.7804</v>
+        <v>1.6634</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6677</v>
+        <v>0.6238</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1863</v>
+        <v>0.1292</v>
       </c>
       <c r="E35" t="n">
-        <v>1.7804</v>
+        <v>1.6634</v>
       </c>
       <c r="F35" t="n">
-        <v>2.5807</v>
+        <v>1.6111</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8003</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.9235</v>
+        <v>1.6111</v>
       </c>
       <c r="I35" t="n">
-        <v>3.0761</v>
+        <v>1.6111</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8003</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="L35" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.2758</v>
+        <v>1.6111</v>
       </c>
       <c r="N35" t="n">
-        <v>259</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.6939</v>
+        <v>1.6578</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6352</v>
+        <v>0.6217</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1469</v>
+        <v>0.1267</v>
       </c>
       <c r="E36" t="n">
-        <v>1.6939</v>
+        <v>1.6578</v>
       </c>
       <c r="F36" t="n">
-        <v>1.6939</v>
+        <v>2.5807</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.8003</v>
       </c>
       <c r="H36" t="n">
-        <v>1.6939</v>
+        <v>2.9235</v>
       </c>
       <c r="I36" t="n">
-        <v>1.6939</v>
+        <v>3.0761</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.8003</v>
       </c>
       <c r="K36" t="n">
-        <v>128</v>
+        <v>195</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M36" t="n">
-        <v>1.6939</v>
+        <v>2.2758</v>
       </c>
       <c r="N36" t="n">
-        <v>128</v>
+        <v>259</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.6376</v>
+        <v>1.5309</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6141</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1213</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>1.6376</v>
+        <v>1.5309</v>
       </c>
       <c r="F37" t="n">
-        <v>1.9076</v>
+        <v>2.3332</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.27</v>
+        <v>-0.531</v>
       </c>
       <c r="H37" t="n">
-        <v>1.9076</v>
+        <v>2.8039</v>
       </c>
       <c r="I37" t="n">
-        <v>1.9076</v>
+        <v>1.5141</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.27</v>
+        <v>-0.531</v>
       </c>
       <c r="K37" t="n">
-        <v>169</v>
+        <v>228</v>
       </c>
       <c r="L37" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>1.6376</v>
+        <v>0.9831</v>
       </c>
       <c r="N37" t="n">
-        <v>228</v>
+        <v>268</v>
       </c>
     </row>
     <row r="38">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.6348</v>
+        <v>1.4827</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6131</v>
+        <v>0.556</v>
       </c>
       <c r="D38" t="n">
-        <v>0.12</v>
+        <v>0.0485</v>
       </c>
       <c r="E38" t="n">
-        <v>1.6348</v>
+        <v>1.4827</v>
       </c>
       <c r="F38" t="n">
         <v>2.1706</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kisserek</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.6111</v>
+        <v>1.4565</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6042</v>
+        <v>0.5462</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1092</v>
+        <v>0.0368</v>
       </c>
       <c r="E39" t="n">
-        <v>1.6111</v>
+        <v>1.4565</v>
       </c>
       <c r="F39" t="n">
-        <v>1.6111</v>
+        <v>1.9076</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="H39" t="n">
-        <v>1.6111</v>
+        <v>1.9076</v>
       </c>
       <c r="I39" t="n">
-        <v>1.6111</v>
+        <v>1.9076</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="K39" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M39" t="n">
-        <v>1.6111</v>
+        <v>1.6376</v>
       </c>
       <c r="N39" t="n">
-        <v>175</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40">
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.4676</v>
+        <v>1.4551</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5504</v>
+        <v>0.5457</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0439</v>
+        <v>0.0361</v>
       </c>
       <c r="E40" t="n">
-        <v>1.4676</v>
+        <v>1.4551</v>
       </c>
       <c r="F40" t="n">
         <v>1.4676</v>
@@ -2286,262 +2286,262 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.4066</v>
+        <v>1.3599</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5275</v>
+        <v>0.51</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0161</v>
+        <v>-0.0064</v>
       </c>
       <c r="E41" t="n">
-        <v>1.4066</v>
+        <v>1.3599</v>
       </c>
       <c r="F41" t="n">
-        <v>1.4066</v>
+        <v>1.3705</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.4066</v>
+        <v>1.3705</v>
       </c>
       <c r="I41" t="n">
-        <v>1.4066</v>
+        <v>1.3705</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.4066</v>
+        <v>1.3705</v>
       </c>
       <c r="N41" t="n">
-        <v>94</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>stressarN</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.3705</v>
+        <v>1.3336</v>
       </c>
       <c r="C42" t="n">
-        <v>0.514</v>
+        <v>0.5001</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0003</v>
+        <v>-0.0181</v>
       </c>
       <c r="E42" t="n">
-        <v>1.3705</v>
+        <v>1.3336</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3705</v>
+        <v>1.2826</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.3705</v>
+        <v>1.2826</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3705</v>
+        <v>1.2826</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.3705</v>
+        <v>1.2826</v>
       </c>
       <c r="N42" t="n">
-        <v>138</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>stressarN</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.2826</v>
+        <v>1.3188</v>
       </c>
       <c r="C43" t="n">
-        <v>0.481</v>
+        <v>0.4946</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0403</v>
+        <v>-0.0247</v>
       </c>
       <c r="E43" t="n">
-        <v>1.2826</v>
+        <v>1.3188</v>
       </c>
       <c r="F43" t="n">
-        <v>1.2826</v>
+        <v>1.4066</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.2826</v>
+        <v>1.4066</v>
       </c>
       <c r="I43" t="n">
-        <v>1.2826</v>
+        <v>1.4066</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>175</v>
+        <v>94</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.2826</v>
+        <v>1.4066</v>
       </c>
       <c r="N43" t="n">
-        <v>175</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8099</v>
+        <v>0.8741</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3037</v>
+        <v>0.3278</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2555</v>
+        <v>-0.2234</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8099</v>
+        <v>0.8741</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8627</v>
+        <v>0.7024</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.0528</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8627</v>
+        <v>0.7024</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9077</v>
+        <v>0.7024</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.0528</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="L44" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8549</v>
+        <v>0.7024</v>
       </c>
       <c r="N44" t="n">
-        <v>259</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7024</v>
+        <v>0.7913</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2634</v>
+        <v>0.2968</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3045</v>
+        <v>-0.2604</v>
       </c>
       <c r="E45" t="n">
-        <v>0.7024</v>
+        <v>0.7913</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7024</v>
+        <v>0.8627</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.0528</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7024</v>
+        <v>0.8627</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7024</v>
+        <v>0.9077</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.0528</v>
       </c>
       <c r="K45" t="n">
-        <v>94</v>
+        <v>195</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M45" t="n">
-        <v>0.7024</v>
+        <v>0.8549</v>
       </c>
       <c r="N45" t="n">
-        <v>94</v>
+        <v>259</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6509</v>
+        <v>0.7601</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2441</v>
+        <v>0.2851</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3279</v>
+        <v>-0.2743</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6509</v>
+        <v>0.7601</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6509</v>
+        <v>0.2807</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6509</v>
+        <v>0.2807</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6509</v>
+        <v>0.2807</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6509</v>
+        <v>0.2807</v>
       </c>
       <c r="N46" t="n">
         <v>82</v>
@@ -2562,47 +2562,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>beastik</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.6959</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2406</v>
+        <v>0.261</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3321</v>
+        <v>-0.303</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.6959</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.6509</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.6509</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.6509</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.6509</v>
       </c>
       <c r="N47" t="n">
-        <v>175</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48">
@@ -2612,16 +2612,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5473</v>
+        <v>0.4875</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2052</v>
+        <v>0.1828</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3751</v>
+        <v>-0.3961</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5473</v>
+        <v>0.4875</v>
       </c>
       <c r="F48" t="n">
         <v>0.5473</v>
@@ -2654,124 +2654,124 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>alex666</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5409</v>
+        <v>0.4438</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2028</v>
+        <v>0.1664</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.378</v>
+        <v>-0.4156</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5409</v>
+        <v>0.4438</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5409</v>
+        <v>0.5356</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5409</v>
+        <v>0.5356</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5409</v>
+        <v>0.5356</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>128</v>
+        <v>191</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5409</v>
+        <v>0.5356</v>
       </c>
       <c r="N49" t="n">
-        <v>128</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>alex666</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5356</v>
+        <v>0.4191</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2009</v>
+        <v>0.1572</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3804</v>
+        <v>-0.4266</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5356</v>
+        <v>0.4191</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5356</v>
+        <v>0.5409</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5356</v>
+        <v>0.5409</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5356</v>
+        <v>0.5409</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>191</v>
+        <v>128</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.5356</v>
+        <v>0.5409</v>
       </c>
       <c r="N50" t="n">
-        <v>191</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MoDo</t>
+          <t>beastik</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4796</v>
+        <v>0.4165</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1799</v>
+        <v>0.1562</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4059</v>
+        <v>-0.4278</v>
       </c>
       <c r="E51" t="n">
-        <v>0.4796</v>
+        <v>0.4165</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4796</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.4796</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4796</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.4796</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="N51" t="n">
         <v>175</v>
@@ -2792,170 +2792,170 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>MoDo</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3319</v>
+        <v>0.318</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1245</v>
+        <v>0.1193</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4731</v>
+        <v>-0.4718</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3319</v>
+        <v>0.318</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3319</v>
+        <v>0.4796</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3319</v>
+        <v>0.4796</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3319</v>
+        <v>0.4796</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3319</v>
+        <v>0.4796</v>
       </c>
       <c r="N52" t="n">
-        <v>91</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3066</v>
+        <v>0.3075</v>
       </c>
       <c r="C53" t="n">
-        <v>0.115</v>
+        <v>0.1153</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4846</v>
+        <v>-0.4765</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3066</v>
+        <v>0.3075</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3066</v>
+        <v>0.1878</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3066</v>
+        <v>0.1878</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3066</v>
+        <v>0.1878</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3066</v>
+        <v>0.1878</v>
       </c>
       <c r="N53" t="n">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2807</v>
+        <v>0.3011</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1053</v>
+        <v>0.1129</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4964</v>
+        <v>-0.4793</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2807</v>
+        <v>0.3011</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2807</v>
+        <v>0.2092</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2807</v>
+        <v>0.2092</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2807</v>
+        <v>0.2092</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2807</v>
+        <v>0.2092</v>
       </c>
       <c r="N54" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.2092</v>
+        <v>0.2311</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0785</v>
+        <v>0.0867</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.529</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2092</v>
+        <v>0.2311</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2092</v>
+        <v>0.3319</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2092</v>
+        <v>0.3319</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2092</v>
+        <v>0.3319</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2092</v>
+        <v>0.3319</v>
       </c>
       <c r="N55" t="n">
         <v>91</v>
@@ -2976,185 +2976,185 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2074</v>
+        <v>0.1817</v>
       </c>
       <c r="C56" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5298</v>
+        <v>-0.5327</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2074</v>
+        <v>0.1817</v>
       </c>
       <c r="F56" t="n">
-        <v>1.1338</v>
+        <v>0.2019</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1.1338</v>
+        <v>0.2019</v>
       </c>
       <c r="I56" t="n">
-        <v>1.193</v>
+        <v>0.2019</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="L56" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.2666000000000001</v>
+        <v>0.2019</v>
       </c>
       <c r="N56" t="n">
-        <v>259</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.2019</v>
+        <v>0.1617</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0757</v>
+        <v>0.0606</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5323</v>
+        <v>-0.5416</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2019</v>
+        <v>0.1617</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2019</v>
+        <v>0.3066</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2019</v>
+        <v>0.3066</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2019</v>
+        <v>0.3066</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2019</v>
+        <v>0.3066</v>
       </c>
       <c r="N57" t="n">
-        <v>94</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.1878</v>
+        <v>0.0618</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0704</v>
+        <v>0.0232</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5387</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1878</v>
+        <v>0.0618</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1878</v>
+        <v>0.0503</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1878</v>
+        <v>0.0503</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1878</v>
+        <v>0.0503</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1878</v>
+        <v>0.0503</v>
       </c>
       <c r="N58" t="n">
-        <v>110</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0503</v>
+        <v>0.0273</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0189</v>
+        <v>0.0102</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-0.6016</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0503</v>
+        <v>0.0273</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0503</v>
+        <v>1.1338</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0503</v>
+        <v>1.1338</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0503</v>
+        <v>1.193</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="K59" t="n">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M59" t="n">
-        <v>0.0503</v>
+        <v>0.2666000000000001</v>
       </c>
       <c r="N59" t="n">
-        <v>91</v>
+        <v>259</v>
       </c>
     </row>
     <row r="60">
@@ -3164,16 +3164,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0412</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0293</v>
+        <v>-0.0155</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.6322</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0412</v>
       </c>
       <c r="F60" t="n">
         <v>-0.07820000000000001</v>
@@ -3210,16 +3210,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.1029</v>
+        <v>-0.1371</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0386</v>
+        <v>-0.0514</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.671</v>
+        <v>-0.6751</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.1029</v>
+        <v>-0.1371</v>
       </c>
       <c r="F61" t="n">
         <v>-0.1029</v>
@@ -3252,185 +3252,185 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>try</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.1189</v>
+        <v>-0.3566</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0446</v>
+        <v>-0.1337</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6783</v>
+        <v>-0.7731</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.1189</v>
+        <v>-0.3566</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.1189</v>
+        <v>-0.3631</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.1189</v>
+        <v>-0.3631</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1189</v>
+        <v>-0.3631</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>163</v>
+        <v>110</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.1189</v>
+        <v>-0.3631</v>
       </c>
       <c r="N62" t="n">
-        <v>163</v>
+        <v>110</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3407</v>
+        <v>-0.391</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1278</v>
+        <v>-0.1466</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7793</v>
+        <v>-0.7885</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3407</v>
+        <v>-0.391</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3407</v>
+        <v>-0.1189</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.3407</v>
+        <v>-0.1189</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3407</v>
+        <v>-0.1189</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>94</v>
+        <v>163</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.3407</v>
+        <v>-0.1189</v>
       </c>
       <c r="N63" t="n">
-        <v>94</v>
+        <v>163</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>try</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3631</v>
+        <v>-0.5303</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1362</v>
+        <v>-0.1989</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7895</v>
+        <v>-0.8507</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.3631</v>
+        <v>-0.5303</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.3631</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.1839</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.3631</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3631</v>
+        <v>-0.2964</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>0.1839</v>
       </c>
       <c r="K64" t="n">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.3631</v>
+        <v>-0.1125</v>
       </c>
       <c r="N64" t="n">
-        <v>110</v>
+        <v>268</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.365</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1369</v>
+        <v>-0.2285</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7904</v>
+        <v>-0.886</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.365</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-0.3407</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1839</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-0.3407</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2964</v>
+        <v>-0.3407</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1839</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>228</v>
+        <v>94</v>
       </c>
       <c r="L65" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.1125</v>
+        <v>-0.3407</v>
       </c>
       <c r="N65" t="n">
-        <v>268</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66">
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4845</v>
+        <v>-0.6508</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1817</v>
+        <v>-0.2441</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8448</v>
+        <v>-0.9045</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4845</v>
+        <v>-0.6508</v>
       </c>
       <c r="F66" t="n">
         <v>-0.4845</v>
@@ -3482,354 +3482,354 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5292</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1985</v>
+        <v>-0.2667</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8651</v>
+        <v>-0.9315</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5292</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5114</v>
+        <v>-0.5827</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.0178</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5114</v>
+        <v>-0.5827</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5114</v>
+        <v>-0.5827</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.0178</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="L67" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5292</v>
+        <v>-0.5827</v>
       </c>
       <c r="N67" t="n">
-        <v>336</v>
+        <v>138</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.5744</v>
+        <v>-0.7975</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2154</v>
+        <v>-0.2991</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8857</v>
+        <v>-0.97</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.5744</v>
+        <v>-0.7975</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.5744</v>
+        <v>-0.6828</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.5744</v>
+        <v>-0.6828</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.5744</v>
+        <v>-0.6828</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.5744</v>
+        <v>-0.6828</v>
       </c>
       <c r="N68" t="n">
-        <v>191</v>
+        <v>138</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>lauNX</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.5827</v>
+        <v>-0.7996</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2185</v>
+        <v>-0.2999</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8895</v>
+        <v>-0.971</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5827</v>
+        <v>-0.7996</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.5827</v>
+        <v>-0.6342</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.5827</v>
+        <v>-0.6342</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5827</v>
+        <v>-0.6342</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.5827</v>
+        <v>-0.6342</v>
       </c>
       <c r="N69" t="n">
-        <v>138</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>lauNX</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6342</v>
+        <v>-0.8077</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2378</v>
+        <v>-0.3029</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9129</v>
+        <v>-0.9746</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6342</v>
+        <v>-0.8077</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.6342</v>
+        <v>-0.5744</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.6342</v>
+        <v>-0.5744</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6342</v>
+        <v>-0.5744</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.6342</v>
+        <v>-0.5744</v>
       </c>
       <c r="N70" t="n">
-        <v>163</v>
+        <v>191</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.8174</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.2425</v>
+        <v>-0.3065</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9186</v>
+        <v>-0.9789</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.8174</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="N71" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6828</v>
+        <v>-0.8245</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.2561</v>
+        <v>-0.3092</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.9821</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6828</v>
+        <v>-0.8245</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6828</v>
+        <v>-0.6978</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6828</v>
+        <v>-0.6978</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6828</v>
+        <v>-0.6978</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6828</v>
+        <v>-0.6978</v>
       </c>
       <c r="N72" t="n">
-        <v>138</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.8708</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.2591</v>
+        <v>-0.3266</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9388</v>
+        <v>-1.0028</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.8708</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.5114</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>-0.0178</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.5114</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.5114</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>-0.0178</v>
       </c>
       <c r="K73" t="n">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.5292</v>
       </c>
       <c r="N73" t="n">
-        <v>128</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.6978</v>
+        <v>-0.8854</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.2617</v>
+        <v>-0.332</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9419</v>
+        <v>-1.0093</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.6978</v>
+        <v>-0.8854</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.6978</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.6978</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.6978</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.6978</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="N74" t="n">
         <v>91</v>
@@ -3850,93 +3850,93 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.7884</v>
+        <v>-0.9046</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.2957</v>
+        <v>-0.3392</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9831</v>
+        <v>-1.0179</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.7884</v>
+        <v>-0.9046</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.7884</v>
+        <v>-0.8141</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.7884</v>
+        <v>-0.8141</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.7884</v>
+        <v>-0.8141</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.7884</v>
+        <v>-0.8141</v>
       </c>
       <c r="N75" t="n">
-        <v>110</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.8141</v>
+        <v>-1.0242</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.3053</v>
+        <v>-0.3841</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9948</v>
+        <v>-1.0713</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.8141</v>
+        <v>-1.0242</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.8141</v>
+        <v>-0.7884</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.8141</v>
+        <v>-0.7884</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8141</v>
+        <v>-0.7884</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>163</v>
+        <v>110</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.8141</v>
+        <v>-0.7884</v>
       </c>
       <c r="N76" t="n">
-        <v>163</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77">
@@ -3946,16 +3946,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.3896</v>
+        <v>-1.5853</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.5211</v>
+        <v>-0.5945</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2568</v>
+        <v>-1.3219</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.3896</v>
+        <v>-1.5853</v>
       </c>
       <c r="F77" t="n">
         <v>-1.3896</v>
@@ -3992,16 +3992,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.8049</v>
+        <v>-2.3754</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.8908</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4458</v>
+        <v>-1.6749</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.8049</v>
+        <v>-2.3754</v>
       </c>
       <c r="F78" t="n">
         <v>-1.8049</v>
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.3088</v>
+        <v>-2.5365</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.8658</v>
+        <v>-0.9512</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.6752</v>
+        <v>-1.7468</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.3088</v>
+        <v>-2.5365</v>
       </c>
       <c r="F79" t="n">
         <v>-2.3088</v>
@@ -4080,93 +4080,93 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>vsm</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.596</v>
+        <v>-2.801</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.9735</v>
+        <v>-1.0504</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.806</v>
+        <v>-1.865</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.596</v>
+        <v>-2.801</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.596</v>
+        <v>-0.1029</v>
       </c>
       <c r="G80" t="n">
-        <v>-1</v>
+        <v>-2.5074</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.596</v>
+        <v>-0.1029</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.596</v>
+        <v>-0.1083</v>
       </c>
       <c r="J80" t="n">
-        <v>-1</v>
+        <v>-2.5074</v>
       </c>
       <c r="K80" t="n">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="L80" t="n">
-        <v>59</v>
+        <v>183</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.596</v>
+        <v>-2.6157</v>
       </c>
       <c r="N80" t="n">
-        <v>228</v>
+        <v>382</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>vsm</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.6103</v>
+        <v>-2.937</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.9789</v>
+        <v>-1.1014</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8125</v>
+        <v>-1.9257</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.6103</v>
+        <v>-2.937</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.1029</v>
+        <v>-1.596</v>
       </c>
       <c r="G81" t="n">
-        <v>-2.5074</v>
+        <v>-1</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.1029</v>
+        <v>-1.596</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1083</v>
+        <v>-1.596</v>
       </c>
       <c r="J81" t="n">
-        <v>-2.5074</v>
+        <v>-1</v>
       </c>
       <c r="K81" t="n">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="L81" t="n">
-        <v>183</v>
+        <v>59</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.6157</v>
+        <v>-2.596</v>
       </c>
       <c r="N81" t="n">
-        <v>382</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -12763,7 +12763,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -13688,7 +13688,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -23443,7 +23443,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -23483,7 +23483,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -23523,7 +23523,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -23563,7 +23563,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -23603,7 +23603,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -23648,7 +23648,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D487" t="n">
@@ -23688,7 +23688,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D488" t="n">
@@ -23728,7 +23728,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D489" t="n">
@@ -23768,7 +23768,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D490" t="n">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D491" t="n">
@@ -23843,7 +23843,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -23883,7 +23883,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -23923,7 +23923,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -23963,7 +23963,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -24003,7 +24003,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D497" t="n">
@@ -24088,7 +24088,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D498" t="n">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D499" t="n">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D500" t="n">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D501" t="n">
@@ -24243,7 +24243,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -24283,7 +24283,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -24323,7 +24323,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -24363,7 +24363,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -24403,7 +24403,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -24448,7 +24448,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D507" t="n">
@@ -24488,7 +24488,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D508" t="n">
@@ -24528,7 +24528,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D509" t="n">
@@ -24568,7 +24568,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D510" t="n">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D511" t="n">
@@ -31448,7 +31448,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D682" t="n">
@@ -31488,7 +31488,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D683" t="n">
@@ -31528,7 +31528,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D684" t="n">
@@ -31568,7 +31568,7 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D685" t="n">
@@ -31608,7 +31608,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D686" t="n">
@@ -31643,7 +31643,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -31683,7 +31683,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -31723,7 +31723,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -31763,7 +31763,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -31803,7 +31803,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -31848,7 +31848,7 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D692" t="n">
@@ -31888,7 +31888,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D693" t="n">
@@ -31928,7 +31928,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D694" t="n">
@@ -31968,7 +31968,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D695" t="n">
@@ -32008,7 +32008,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D696" t="n">
@@ -32043,7 +32043,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -32083,7 +32083,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -32123,7 +32123,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -32163,7 +32163,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -32203,7 +32203,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -32248,7 +32248,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D702" t="n">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D703" t="n">
@@ -32328,7 +32328,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D704" t="n">
@@ -32368,7 +32368,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D705" t="n">
@@ -32408,7 +32408,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D706" t="n">
@@ -32443,7 +32443,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -32483,7 +32483,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -32523,7 +32523,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -32563,7 +32563,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -32603,7 +32603,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
